--- a/personal_trainer_forms/008_personal_trainer_feedback_form--personal_trainer_forms.xlsx
+++ b/personal_trainer_forms/008_personal_trainer_feedback_form--personal_trainer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'traditional'}</t>
+          <t>traditional</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Traditional'}</t>
+          <t>Traditional</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'unhelpful'}</t>
+          <t>unhelpful</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Unhelpful'}</t>
+          <t>Unhelpful</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_helpful'}</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Helpful'}</t>
+          <t>Somewhat Helpful</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very Helpful'}</t>
+          <t>Very Helpful</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'unprofessional'}</t>
+          <t>unprofessional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Unprofessional'}</t>
+          <t>Unprofessional</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_professional'}</t>
+          <t>somewhat_professional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Professional'}</t>
+          <t>Somewhat Professional</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_professional'}</t>
+          <t>very_professional</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very Professional'}</t>
+          <t>Very Professional</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
